--- a/data/documents/xlsx/yield_tracker.xlsx
+++ b/data/documents/xlsx/yield_tracker.xlsx
@@ -1,14 +1,415 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet name="yield_tracker" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yield_tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
 </workbook>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -65,7 +466,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-01-13</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -73,7 +474,7 @@
           <t>40.8%</t>
         </is>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>342</v>
       </c>
       <c r="F2" t="inlineStr">
@@ -105,7 +506,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-01-13</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -113,7 +514,7 @@
           <t>41.5%</t>
         </is>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>335</v>
       </c>
       <c r="F3" t="inlineStr">
@@ -145,7 +546,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -153,7 +554,7 @@
           <t>41.2%</t>
         </is>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>339</v>
       </c>
       <c r="F4" t="inlineStr">
@@ -185,7 +586,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -193,7 +594,7 @@
           <t>40.9%</t>
         </is>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>348</v>
       </c>
       <c r="F5" t="inlineStr">
@@ -225,7 +626,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-01-20</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -233,7 +634,7 @@
           <t>42.1%</t>
         </is>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>328</v>
       </c>
       <c r="F6" t="inlineStr">
@@ -248,7 +649,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Lot 2 baseline; confirms systematic fab issue</t>
+          <t>Lot 2 baseline; confirms systematic fab issue; qual lot 1 of 3 for HTOL</t>
         </is>
       </c>
     </row>
@@ -265,7 +666,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-01-20</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -273,7 +674,7 @@
           <t>41.8%</t>
         </is>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>331</v>
       </c>
       <c r="F7" t="inlineStr">
@@ -305,7 +706,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -313,7 +714,7 @@
           <t>43.4%</t>
         </is>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>315</v>
       </c>
       <c r="F8" t="inlineStr">
@@ -345,7 +746,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -353,7 +754,7 @@
           <t>43.0%</t>
         </is>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>319</v>
       </c>
       <c r="F9" t="inlineStr">
@@ -368,7 +769,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Packaged units assigned to Kevin for qual</t>
+          <t>Qual lot 2 of 3: packaged units assigned to Kevin for HTOL</t>
         </is>
       </c>
     </row>
@@ -385,7 +786,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -393,7 +794,7 @@
           <t>54.8%</t>
         </is>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>182</v>
       </c>
       <c r="F10" t="inlineStr">
@@ -425,7 +826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -433,7 +834,7 @@
           <t>55.2%</t>
         </is>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>178</v>
       </c>
       <c r="F11" t="inlineStr">
@@ -465,7 +866,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -473,7 +874,7 @@
           <t>54.5%</t>
         </is>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
@@ -488,7 +889,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Packaged units loaded to HTOL chamber</t>
+          <t>Qual lot 3 of 3: 77 units to HTOL (U155-U231); U162/U189/U215 fail at 500h</t>
         </is>
       </c>
     </row>
@@ -505,7 +906,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -513,7 +914,7 @@
           <t>55.1%</t>
         </is>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>180</v>
       </c>
       <c r="F13" t="inlineStr">
@@ -545,7 +946,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -553,7 +954,7 @@
           <t>55.4%</t>
         </is>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>176</v>
       </c>
       <c r="F14" t="inlineStr">
@@ -585,7 +986,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -593,7 +994,7 @@
           <t>55.8%</t>
         </is>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>172</v>
       </c>
       <c r="F15" t="inlineStr">
@@ -625,7 +1026,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -633,7 +1034,7 @@
           <t>56.1%</t>
         </is>
       </c>
-      <c r="E16">
+      <c r="E16" t="n">
         <v>169</v>
       </c>
       <c r="F16" t="inlineStr">
@@ -665,7 +1066,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -673,7 +1074,7 @@
           <t>56.4%</t>
         </is>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>165</v>
       </c>
       <c r="F17" t="inlineStr">
@@ -688,7 +1089,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>HTOL test lot; later suffers 500h fail</t>
+          <t>Rev A production lot; IO leakage now the main limiter</t>
         </is>
       </c>
     </row>
@@ -705,7 +1106,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -713,7 +1114,7 @@
           <t>56.7%</t>
         </is>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>162</v>
       </c>
       <c r="F18" t="inlineStr">
@@ -728,7 +1129,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Failures traced to undersized ESD clamp</t>
+          <t>Bin 7 leakage traced to undersized ESD clamp</t>
         </is>
       </c>
     </row>
@@ -745,7 +1146,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -753,7 +1154,7 @@
           <t>57.0%</t>
         </is>
       </c>
-      <c r="E19">
+      <c r="E19" t="n">
         <v>158</v>
       </c>
       <c r="F19" t="inlineStr">
@@ -785,7 +1186,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -793,7 +1194,7 @@
           <t>57.4%</t>
         </is>
       </c>
-      <c r="E20">
+      <c r="E20" t="n">
         <v>154</v>
       </c>
       <c r="F20" t="inlineStr">
@@ -825,7 +1226,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -833,7 +1234,7 @@
           <t>57.8%</t>
         </is>
       </c>
-      <c r="E21">
+      <c r="E21" t="n">
         <v>150</v>
       </c>
       <c r="F21" t="inlineStr">
@@ -865,7 +1266,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -873,7 +1274,7 @@
           <t>57.9%</t>
         </is>
       </c>
-      <c r="E22">
+      <c r="E22" t="n">
         <v>148</v>
       </c>
       <c r="F22" t="inlineStr">
@@ -905,7 +1306,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -913,7 +1314,7 @@
           <t>58.2%</t>
         </is>
       </c>
-      <c r="E23">
+      <c r="E23" t="n">
         <v>145</v>
       </c>
       <c r="F23" t="inlineStr">
@@ -945,7 +1346,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -953,7 +1354,7 @@
           <t>78.4%</t>
         </is>
       </c>
-      <c r="E24">
+      <c r="E24" t="n">
         <v>48</v>
       </c>
       <c r="F24" t="inlineStr">
@@ -985,7 +1386,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -993,7 +1394,7 @@
           <t>78.7%</t>
         </is>
       </c>
-      <c r="E25">
+      <c r="E25" t="n">
         <v>46</v>
       </c>
       <c r="F25" t="inlineStr">
@@ -1025,7 +1426,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1033,7 +1434,7 @@
           <t>78.2%</t>
         </is>
       </c>
-      <c r="E26">
+      <c r="E26" t="n">
         <v>49</v>
       </c>
       <c r="F26" t="inlineStr">
@@ -1065,7 +1466,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1073,7 +1474,7 @@
           <t>79.1%</t>
         </is>
       </c>
-      <c r="E27">
+      <c r="E27" t="n">
         <v>44</v>
       </c>
       <c r="F27" t="inlineStr">
@@ -1105,7 +1506,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1113,7 +1514,7 @@
           <t>79.5%</t>
         </is>
       </c>
-      <c r="E28">
+      <c r="E28" t="n">
         <v>42</v>
       </c>
       <c r="F28" t="inlineStr">
@@ -1145,7 +1546,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1153,7 +1554,7 @@
           <t>80.2%</t>
         </is>
       </c>
-      <c r="E29">
+      <c r="E29" t="n">
         <v>38</v>
       </c>
       <c r="F29" t="inlineStr">
@@ -1185,7 +1586,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1193,7 +1594,7 @@
           <t>81.0%</t>
         </is>
       </c>
-      <c r="E30">
+      <c r="E30" t="n">
         <v>35</v>
       </c>
       <c r="F30" t="inlineStr">
@@ -1225,7 +1626,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1233,7 +1634,7 @@
           <t>82.1%</t>
         </is>
       </c>
-      <c r="E31">
+      <c r="E31" t="n">
         <v>31</v>
       </c>
       <c r="F31" t="inlineStr">
@@ -1265,7 +1666,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1273,7 +1674,7 @@
           <t>82.3%</t>
         </is>
       </c>
-      <c r="E32">
+      <c r="E32" t="n">
         <v>29</v>
       </c>
       <c r="F32" t="inlineStr">
@@ -1305,7 +1706,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1313,7 +1714,7 @@
           <t>82.5%</t>
         </is>
       </c>
-      <c r="E33">
+      <c r="E33" t="n">
         <v>28</v>
       </c>
       <c r="F33" t="inlineStr">
@@ -1332,6 +1733,207 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>LOT-V7-030</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>W01</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>82.8%</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>27</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Random Particle Defect</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>B1:82.8%, B2:1.3%, B4:4.4%, B7:9.0%, B9:2.5%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>First full-production lot after PSW</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>LOT-V7-034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>W01</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>83.1%</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>26</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Random Oxide Pinhole</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>B1:83.1%, B2:1.3%, B4:4.4%, B7:9.0%, B9:2.2%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Halvorsen second-source slurry in production</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>LOT-V7-038</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>W01</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>83.0%</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>26</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Micro-Scratch M4</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>B1:83.0%, B2:1.3%, B4:4.4%, B7:9.0%, B9:2.3%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Meridian leadframe lots enter backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>LOT-V7-042</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>W01</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>83.4%</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>25</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Random Particle Defect</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>B1:83.4%, B2:1.3%, B4:4.4%, B7:9.0%, B9:1.9%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>200k units/month run rate reached</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>LOT-V7-046</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>W01</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>83.2%</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>25</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Wafer Edge EBR Residue</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>B1:83.2%, B2:1.3%, B4:4.4%, B7:9.0%, B9:2.1%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Steady-state production baseline</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>